--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L162: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (Vancouver News-Advertiserã€‚ He really quite as much had been entered into for the-</t>
+          <t>L162: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP :: (Vancouver News-Advertiser。 He really quite as much had been entered into for the-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L26: isolated marker/symbol line :: -</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>594</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,12 +704,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L248: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -775,12 +779,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Welsford, Aug. 4â€”The Better Farm-</t>
+          <t>L454: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -826,12 +830,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -850,12 +854,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Gagetown, Aug. 2.â€”Mr. and Mrs.</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -881,7 +885,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L377: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 000000000</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -919,14 +927,10 @@
           <t>L186: suspicious token(s): 1deli (letter/digit mix) :: evening, at which Mr. Hazen was to the a 1deli theto have come here to sources, concluded the Minister.</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moosejaw, Sask., Aug. 4.â€” The City</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: No. 19â€”Extra Long Corset with</t>
+          <t>L209: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: •*.117.11.The by the resources of the province, and</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -990,14 +994,10 @@
           <t>L193: suspicious token(s): VancouFederal (odd internal casing) :: rank and file of the party in VancouFederal House, e had in ended comgether to build up one of the greatest "I</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€Œ</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: No. 22â€” Medium Length Corset</t>
+          <t>L261: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: No. 14â€”Medium Length Corset,</t>
+          <t>L377: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 000000000</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Government will be Carried Outâ€”First Ministerial State-</t>
+          <t>L383: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ment on Subject Since Prorogationâ€”Sir Richard Mc-</t>
+          <t>L518: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1243,11 +1243,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ask your neighbors about Deering Machines. They will tell you thatâ€”</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1257,7 +1253,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1279,12 +1275,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1302,11 +1298,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: there are none better.â€”</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1361,11 +1353,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L179: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock, and left onthe return to Vic-1 T.as he result of a expenditure on the harbor here he</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1402,7 +1390,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1420,11 +1408,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L209: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*.117.11.The by the resources of the province, and</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1479,16 +1463,12 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L210: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜For Heâ€™s a Jolly Good Fellow. The 3 1 '. 11 late and</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L248: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1538,11 +1518,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nowâ€™s the time to Preserve them.</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1597,11 +1573,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Polinin severâ€� :</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1644,11 +1616,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1691,11 +1659,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L360: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Welsford, Aug. 4â€”The Better Farm-</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1738,11 +1702,7 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 000000000</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1785,11 +1745,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1799,7 +1755,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L261: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1832,11 +1788,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: pireâ€™s greatest defence.</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1875,11 +1827,7 @@
       </c>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L428: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: adaâ€™s due to the King and to the coun ill.</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -1918,11 +1866,7 @@
       </c>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -1932,7 +1876,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L379: symbol-only separator/garbage line :: 6662626</t>
+          <t>L377: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 000000000</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1961,11 +1905,7 @@
       </c>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Canadaâ€™s Defence.</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -1975,7 +1915,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L384: isolated marker/symbol line :: @</t>
+          <t>L379: symbol-only separator/garbage line :: 6662626</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2004,21 +1944,17 @@
       </c>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L529: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Empire defence he meant Canadaâ€™s</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L454: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L388: isolated marker/symbol line :: G</t>
+          <t>L383: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2047,11 +1983,7 @@
       </c>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mocsejaw, Sask., Aug. 4.â€”The City</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2061,7 +1993,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L389: isolated marker/symbol line :: @</t>
+          <t>L384: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2090,11 +2022,7 @@
       </c>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Duties.â€”Six months residence upon</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2104,7 +2032,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L390: isolated marker/symbol line :: 0</t>
+          <t>L388: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2129,11 +2057,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Duties.â€”Must reside upon the home-</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2143,7 +2067,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L391: isolated marker/symbol line :: 9</t>
+          <t>L389: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2168,21 +2092,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Unauthorized publication of this</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L669: isolated marker/symbol line :: A</t>
+          <t>L606: isolated marker/symbol line :: 「</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: 0</t>
+          <t>L390: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2207,21 +2127,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Vancouver, Aug. 4â€”Four thousand</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L715: isolated marker/symbol line :: L</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L393: isolated marker/symbol line :: :</t>
+          <t>L391: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2249,10 +2165,14 @@
       <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>L669: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L394: isolated marker/symbol line :: 0</t>
+          <t>L392: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2280,10 +2200,14 @@
       <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>L715: isolated marker/symbol line :: L</t>
+        </is>
+      </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: @</t>
+          <t>L393: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2314,7 +2238,7 @@
       <c r="N34" s="1" t="inlineStr"/>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L396: isolated marker/symbol line :: @</t>
+          <t>L394: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2345,7 +2269,7 @@
       <c r="N35" s="1" t="inlineStr"/>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: 0</t>
+          <t>L395: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2376,7 +2300,7 @@
       <c r="N36" s="1" t="inlineStr"/>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: @</t>
+          <t>L396: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2407,7 +2331,7 @@
       <c r="N37" s="1" t="inlineStr"/>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L399: isolated marker/symbol line :: :</t>
+          <t>L397: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2438,7 +2362,7 @@
       <c r="N38" s="1" t="inlineStr"/>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L400: isolated marker/symbol line :: @</t>
+          <t>L398: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2469,7 +2393,7 @@
       <c r="N39" s="1" t="inlineStr"/>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L401: isolated marker/symbol line :: I</t>
+          <t>L399: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2500,7 +2424,7 @@
       <c r="N40" s="1" t="inlineStr"/>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: 0</t>
+          <t>L400: isolated marker/symbol line :: @</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2531,7 +2455,7 @@
       <c r="N41" s="1" t="inlineStr"/>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L403: isolated marker/symbol line :: 0</t>
+          <t>L401: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2562,7 +2486,7 @@
       <c r="N42" s="1" t="inlineStr"/>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L421: isolated marker/symbol line :: I</t>
+          <t>L402: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2593,7 +2517,7 @@
       <c r="N43" s="1" t="inlineStr"/>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L422: isolated marker/symbol line :: 6</t>
+          <t>L403: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2624,7 +2548,7 @@
       <c r="N44" s="1" t="inlineStr"/>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: 30</t>
+          <t>L421: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2655,7 +2579,7 @@
       <c r="N45" s="1" t="inlineStr"/>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L422: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2686,7 +2610,7 @@
       <c r="N46" s="1" t="inlineStr"/>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L613: isolated marker/symbol line :: 1</t>
+          <t>L516: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2717,7 +2641,7 @@
       <c r="N47" s="1" t="inlineStr"/>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L703: isolated marker/symbol line :: I</t>
+          <t>L518: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -2748,7 +2672,7 @@
       <c r="N48" s="1" t="inlineStr"/>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L715: isolated marker/symbol line :: 2</t>
+          <t>L613: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -2779,7 +2703,7 @@
       <c r="N49" s="1" t="inlineStr"/>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: r</t>
+          <t>L703: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -2810,7 +2734,7 @@
       <c r="N50" s="1" t="inlineStr"/>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L867: isolated marker/symbol line :: r</t>
+          <t>L715: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -2841,7 +2765,7 @@
       <c r="N51" s="1" t="inlineStr"/>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L877: isolated marker/symbol line :: 1</t>
+          <t>L809: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -2855,6 +2779,68 @@
       <c r="X51" s="1" t="inlineStr"/>
       <c r="Y51" s="1" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr"/>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L867: isolated marker/symbol line :: r</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr"/>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L877: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
